--- a/per-stock/TSEM/financials.xlsx
+++ b/per-stock/TSEM/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32600614912</v>
+        <v>34118912000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29497591808</v>
+        <v>30933909504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>126.84259</v>
+        <v>133.36743</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47.74835</v>
+        <v>49.972115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20.104414</v>
+        <v>21.04073</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>128945128</v>
+        <v>322147000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>273.98</v>
+        <v>286.74</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D48</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C48</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B48</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D46</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C46</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B46</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B40:E40)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B36:E36)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B4:E4)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1792,13 +2272,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1808,6 +2288,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1818,30 +2299,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1854,10 +2340,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>135841.915551</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -1866,9 +2352,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>47429.239595</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1877,21 +2364,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.087982</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.018452</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.124855</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.159625</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.086882</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.039263</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1900,21 +2388,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>147490000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>191128000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>127036000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>114501000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>107126000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>157443000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1922,18 +2411,19 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
         <v>7362000</v>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
         <v>1208000</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1943,18 +2433,19 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n">
         <v>7362000</v>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
         <v>1208000</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1965,21 +2456,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>65032000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>80132000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>53645000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>46551000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>40142000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>55138000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1988,21 +2480,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>82925000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>77792000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>76456000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>74636000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>74228000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>75820000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2011,21 +2504,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>302680000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>322594000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>302622000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>292035000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>284999000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>300338000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2034,21 +2528,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>147490000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>198490000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>127036000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>114501000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>107126000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>158651000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2057,21 +2552,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>64565000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>120698000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>50580000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>39865000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>32898000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>82831000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2080,21 +2576,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>9518000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>13900000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>10491000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>14387000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>10598000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>31828000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2102,16 +2599,19 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>9518000</v>
+      </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n">
         <v>14387000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>10598000</v>
       </c>
-      <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2120,21 +2620,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>65032000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>72905841.91555101</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>53645000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>46551000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>40142000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>53977429.239595</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2143,21 +2644,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>65032000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>80132000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>53645000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>46551000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>40142000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>55138000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2166,21 +2668,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>349066000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>369377000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>345087000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>332196000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>325272000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>340772000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2189,21 +2692,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>64565000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>70829000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>50580000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>39865000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>32898000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>46419000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2212,21 +2716,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>114342000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>114191000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>113751000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>113282000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>113152000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>112967000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2235,21 +2740,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>112564000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>112396000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>112132000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>111810000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>111575000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>111493000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2258,21 +2764,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.41</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>0.49</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2281,21 +2788,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.42</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.36</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0.49</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2304,21 +2812,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>65032000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>80132000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>53645000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>46551000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>40142000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>55138000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2327,21 +2836,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>65032000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>80132000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>53645000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>46551000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>40142000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>55138000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2350,21 +2860,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>65032000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>80132000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>53645000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>46551000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>40142000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>55138000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2373,21 +2884,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-2533000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>73000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>199000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>959000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>425000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>2553000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2396,21 +2908,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>67565000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>80059000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>53446000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>45592000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>39717000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>52585000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2419,21 +2932,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>67565000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>80059000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>53446000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>45592000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>39717000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>52585000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2442,21 +2956,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>6518000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>1505000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>7625000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>8660000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>3779000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>2149000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2465,21 +2980,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>74083000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>81564000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>61071000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>54252000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>43496000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>54734000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2491,10 +3007,11 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
         <v>-23513000</v>
       </c>
-      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2502,20 +3019,21 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2523,20 +3041,21 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2545,21 +3064,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>9518000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>13900000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>10491000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>14387000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>10598000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>31828000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2567,18 +3087,19 @@
           <t>Total Other Finance Cost</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n">
         <v>36234000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-10491000</v>
       </c>
-      <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
         <v>19631000</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>-6104000</v>
       </c>
     </row>
@@ -2588,16 +3109,19 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
+      <c r="B35" s="3" t="n">
+        <v>9518000</v>
+      </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n">
         <v>14387000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>10598000</v>
       </c>
-      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2606,21 +3130,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>64565000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>70829000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>50580000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>39865000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>32898000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>46419000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2629,21 +3154,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>46386000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>46783000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>42465000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>40161000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>40273000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>40434000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2652,21 +3178,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>23530000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>24850000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>22056000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>19418000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>20172000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>20622000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2675,21 +3202,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>22856000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>21933000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>20409000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>20743000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>20101000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>19812000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2698,21 +3226,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>110951000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>117612000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>93045000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>80026000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>73171000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>86853000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2721,21 +3250,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>302680000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>322594000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>302622000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>292035000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>284999000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>300338000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2744,21 +3274,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>413631000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>440206000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>395667000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>372061000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>358170000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>387191000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2767,28 +3298,29 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>413631000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>440206000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>395667000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>372061000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>358170000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>387191000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4404,7 +4936,1697 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>86667</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>86667</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>86667</v>
+      </c>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n">
+        <v>86667</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>87000</v>
+      </c>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>112824944</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>112534333</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>112123800</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>111845587</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>111756623</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>112911611</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>112621000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>112210467</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>111845587</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>111843290</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>155856000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>161518000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>164087000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>176097000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>162325000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2988804000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2908306000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2845720000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2778149000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2715153000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>155856000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3080805000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>164087000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>176097000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>162325000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1668578000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1445875000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1510319000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1494997000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1478799000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2988804000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2908306000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2845720000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2778149000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2715153000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2988804000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2919287000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2845720000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2787575000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2715153000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3119552000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>3052693000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2976603000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2930593000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2849988000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2974100000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2904583000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2832582000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2774437000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2702015000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n">
+        <v>-14704000</v>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n">
+        <v>-13138000</v>
+      </c>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2988804000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2919287000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2845720000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2787575000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2715153000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n">
+        <v>274319000</v>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n">
+        <v>236551000</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n">
+        <v>-66457000</v>
+      </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n">
+        <v>-74188000</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n">
+        <v>-66457000</v>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
+        <v>-74188000</v>
+      </c>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n">
+        <v>9072000</v>
+      </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n">
+        <v>9072000</v>
+      </c>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n">
+        <v>895949000</v>
+      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n">
+        <v>675479000</v>
+      </c>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n">
+        <v>1373643000</v>
+      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n">
+        <v>1377986000</v>
+      </c>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>450905000</v>
+      </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>446562000</v>
+      </c>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n">
+        <v>450905000</v>
+      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n">
+        <v>446562000</v>
+      </c>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>726520000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>417707000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>420020000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>428973000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>406590000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>366157000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>153960000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>150778000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>160652000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>157128000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>19996000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>12174000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>19895000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>17634000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>22293000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>6448000</v>
+      </c>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>4985000</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>215413000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1932000</v>
+      </c>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>7690000</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>10122000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>215413000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1932000</v>
+      </c>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
+        <v>7690000</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>10122000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>12174000</v>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>10129000</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>130748000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>133406000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>130883000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>143018000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>134835000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>130748000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>133406000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>130883000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>143018000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>134835000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>360363000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>263747000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>269242000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>268321000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>249462000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>86899000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>3929000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>84206000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>83964000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>86421000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>127307000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>25581000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>19926000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>15592000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>17233000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>127307000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>25581000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>19926000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>15592000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>17233000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>25108000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>28112000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>33204000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>33079000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>27490000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>25108000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>28112000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>33204000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>33079000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>27490000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>70299000</v>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
+        <v>65199000</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>121049000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>135826000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>131906000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>135686000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>118318000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>121049000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>135826000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>131906000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>135686000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>118318000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Other Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>4806000</v>
+      </c>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>5070000</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
+        <v>7105000</v>
+      </c>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n">
+        <v>12428000</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>121049000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>123915000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>131906000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>135686000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>118318000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>3700620000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3322290000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3252602000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>3203410000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>3108605000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1671679000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1612668000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1473041000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1440092000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1380344000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>142398000</v>
+      </c>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n">
+        <v>32803000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>27951000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>34131000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n">
+        <v>39526000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Defined Pension Benefit</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n">
+        <v>1810000</v>
+      </c>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n">
+        <v>1870000</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n">
+        <v>1336000</v>
+      </c>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n">
+        <v>2514000</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n">
+        <v>13354000</v>
+      </c>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n">
+        <v>1768000</v>
+      </c>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="3" t="n">
+        <v>13354000</v>
+      </c>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n">
+        <v>1768000</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n">
+        <v>4427000</v>
+      </c>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n">
+        <v>6780000</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n">
+        <v>4427000</v>
+      </c>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>6780000</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>6780000</v>
+      </c>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>10981000</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n">
+        <v>9426000</v>
+      </c>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>12768000</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>10770000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n">
+        <v>3981000</v>
+      </c>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
+        <v>5768000</v>
+      </c>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>1529281000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1580760000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1440238000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1402715000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1346213000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>-3722630000</v>
+      </c>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>-3458759000</v>
+      </c>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>5303390000</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>4753255000</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n">
+        <v>117704000</v>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>7874000</v>
+      </c>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n">
+        <v>4694587000</v>
+      </c>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n">
+        <v>4281817000</v>
+      </c>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n">
+        <v>491099000</v>
+      </c>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n">
+        <v>463564000</v>
+      </c>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>2028941000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1709622000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1779561000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1763318000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1728261000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>61720000</v>
+      </c>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>56564000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>53652000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>51429000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n">
+        <v>41104000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n">
+        <v>21928000</v>
+      </c>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n">
+        <v>32985000</v>
+      </c>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>254833000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>256855000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>286682000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>286747000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>276072000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v>7181000</v>
+      </c>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n">
+        <v>22482000</v>
+      </c>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n">
+        <v>144373000</v>
+      </c>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n">
+        <v>118642000</v>
+      </c>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n">
+        <v>105301000</v>
+      </c>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n">
+        <v>127171000</v>
+      </c>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>213840000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>278929000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>213013000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>215316000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>219496000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n">
+        <v>14937000</v>
+      </c>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>1281000</v>
+      </c>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n">
+        <v>41197000</v>
+      </c>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n">
+        <v>27551000</v>
+      </c>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>213840000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>222795000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>213013000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>215316000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>219496000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n">
+        <v>-4602000</v>
+      </c>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n">
+        <v>-4982000</v>
+      </c>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n">
+        <v>227397000</v>
+      </c>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n">
+        <v>216914000</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>1498548000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>1151910000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1223302000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>1207603000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1181264000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>1255239000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>916541000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>950560000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>942310000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>906446000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>243309000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>235369000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>272742000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>265293000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>274818000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5350,13 +7572,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5366,6 +7588,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5376,30 +7599,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5412,21 +7640,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>353601000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-79304000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>35933000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>11917000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-17489000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>2920000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5434,18 +7663,19 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n">
         <v>-18516000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-6875000</v>
       </c>
-      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n">
         <v>-79017000</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>-16402000</v>
       </c>
     </row>
@@ -5456,21 +7686,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-156368000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-118842000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-103490000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-110682000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-111411000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-97896000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5479,21 +7710,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>243309000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>235369000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>272742000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>265293000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>274818000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>271894000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5502,21 +7734,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>235369000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>272742000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>265293000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>274818000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>271894000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>270979000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5525,21 +7758,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-1080000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-3225000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-1609000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>1454000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>2817000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-4972000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5548,21 +7782,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>9020000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>-34148000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>9058000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>-10979000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>107000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>5887000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5571,21 +7806,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-4581000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>-4708000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>-6875000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>5104000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>-26874000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>2795000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5594,21 +7830,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-4581000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-4708000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-6875000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>5104000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-26874000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>2795000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5617,21 +7854,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-4581000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-4708000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-6875000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>5104000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-26874000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>2795000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5639,18 +7877,19 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n">
         <v>-4708000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-6875000</v>
       </c>
-      <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n">
         <v>2795000</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H12" s="3" t="n">
         <v>-16402000</v>
       </c>
     </row>
@@ -5660,18 +7899,19 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n">
         <v>-18516000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-6875000</v>
       </c>
-      <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n">
         <v>-79017000</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>-16402000</v>
       </c>
     </row>
@@ -5682,21 +7922,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-496368000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-68978000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-123490000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-138682000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-66941000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-97724000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5705,21 +7946,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-496368000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-68978000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-123490000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-138682000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-66941000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-97724000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5728,21 +7970,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-340000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>42000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-28000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>44470000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-3798000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5755,7 +7998,8 @@
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n">
         <v>19412000</v>
       </c>
     </row>
@@ -5766,21 +8010,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-156368000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-110978000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-103490000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-110682000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-111411000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-93396000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5789,21 +8034,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-156368000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-118842000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-103490000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-110682000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-111411000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-97896000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5812,21 +8058,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>509969000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>39538000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>139423000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>122599000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>93922000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>100816000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5835,21 +8082,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>509969000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>39538000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>139423000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>122599000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>93922000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>100816000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5858,21 +8106,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>71256000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-124845000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>9643000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-1188000</v>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>-20581000</v>
-      </c>
       <c r="F22" s="3" t="n">
-        <v>-40161000</v>
+        <v>-17268000</v>
       </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5881,21 +8130,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>30091000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>19227000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>4223000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-7297000</v>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>-4432000</v>
-      </c>
       <c r="F23" s="3" t="n">
-        <v>9997000</v>
+        <v>-1119000</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5904,21 +8154,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-470000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-16988000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>5296000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>5666000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-175000</v>
       </c>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n">
-        <v>-3298000</v>
-      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5927,21 +8178,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>23578000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-137076000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>6770000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-5002000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>5622000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-36464000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5950,21 +8202,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>8722000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-4695000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-6516000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>8218000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-11114000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>18320000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5973,21 +8226,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>8722000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-4695000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-6516000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>8218000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-11114000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>18320000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5996,21 +8250,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>8722000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-4695000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-6516000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>8218000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-11114000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>18320000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6019,21 +8274,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>769000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>25656000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-1983000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-7745000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-4128000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-3356000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6042,21 +8298,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>8566000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-10969000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>1853000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>4972000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-6354000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-19167000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6065,21 +8322,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>8566000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-10969000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>1853000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>4972000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-6354000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-19167000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6088,21 +8346,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>288223000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>6532000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-122000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>3559000</v>
       </c>
-      <c r="E32" s="3" t="n">
-        <v>558000</v>
-      </c>
       <c r="F32" s="3" t="n">
-        <v>12439000</v>
+        <v>-2755000</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6111,21 +8370,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>82925000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>77792000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>76456000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>74636000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>74228000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>75820000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6134,21 +8394,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>82925000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>77792000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>76456000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>74636000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>74228000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>75820000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6160,10 +8421,11 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
         <v>-294000</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="H35" s="3" t="n">
         <v>-425000</v>
       </c>
     </row>
@@ -6177,10 +8439,11 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n">
         <v>-294000</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="H36" s="3" t="n">
         <v>-425000</v>
       </c>
     </row>
@@ -6191,28 +8454,29 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>67565000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>80059000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>53446000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>45592000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>39717000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>52585000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
